--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R652159c5a9354457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f4c766a9b994b85"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3f4c766a9b994b85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R03df67b136dd44d6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R03df67b136dd44d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rba382b36b32b4127"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rba382b36b32b4127"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3834b6b0c013449b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3834b6b0c013449b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83ac7b082f2b4887"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83ac7b082f2b4887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62ed313d93cc4207"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62ed313d93cc4207"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R06cefea955e84d5b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R06cefea955e84d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e82e2ead2914db8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e82e2ead2914db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R41420584da8b4234"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R41420584da8b4234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2318a02c97364bb0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2318a02c97364bb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd6055f19f73e4c62"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DataBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd6055f19f73e4c62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R763b1697bc7a404b"/>
   </x:sheets>
 </x:workbook>
 </file>
